--- a/output/screener_output.xlsx
+++ b/output/screener_output.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:AE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -459,16 +459,17 @@
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="7" customWidth="1" min="22" max="22"/>
-    <col width="19" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="33" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
     <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="21" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,50 +575,55 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>return_on_capital_employed_pct</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>broad_sector</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>id_y</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>market_cap_crore</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>enterprise_value_crore</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>pb_ratio</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ev_ebitda</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dividend_yield_pct</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>net_profit</t>
         </is>
@@ -683,36 +689,39 @@
       <c r="T2" t="n">
         <v>88.88</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>5640.87982832618</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>282</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>1040632.92</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>1061542.29</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>76.23</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>7.87</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>24.64</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>4.27</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>68904</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>8167</v>
       </c>
     </row>
@@ -776,36 +785,39 @@
       <c r="T3" t="n">
         <v>83.98</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>65.26850065983149</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>522</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>461188.15</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>542230.13</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>78.69</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>6.08</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>29.94</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>240893</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>46099</v>
       </c>
     </row>
@@ -869,36 +881,39 @@
       <c r="T4" t="n">
         <v>67.98999999999999</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>35.77492689368928</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>54</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>2126725.18</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>2475080.63</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>73.37</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>3.9</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>23.94</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>2.42</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>35495</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>5558</v>
       </c>
     </row>
@@ -962,36 +977,39 @@
       <c r="T5" t="n">
         <v>66.73</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>15.24626398560363</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>30</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>675598.01</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>611165.74</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>48.9</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>2.31</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>31.76</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>1.16</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>26711</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>8104</v>
       </c>
     </row>
@@ -1055,36 +1073,39 @@
       <c r="T6" t="n">
         <v>66.23</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>19.44697569501501</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>492</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>1339586.09</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>1264175.16</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>37.9</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>6.71</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>21.41</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>3.88</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>48497</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>9610</v>
       </c>
     </row>
@@ -1142,36 +1163,39 @@
       <c r="T7" t="n">
         <v>64.38</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>23.44105657077455</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>36</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>1372183.55</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>1357949.64</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>44.57</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>9.91</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>24.76</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>50351</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>20829</v>
       </c>
     </row>
@@ -1235,36 +1259,39 @@
       <c r="T8" t="n">
         <v>63.74</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>5.220349505440574</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>264</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>1319221.86</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>1598760.1</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>25.76</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>6.2</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>38.28</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>3.43</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>159516</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>46081</v>
       </c>
     </row>
@@ -1325,36 +1352,39 @@
       <c r="T9" t="n">
         <v>62.12</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>37.75589530966572</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>294</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>1112279.92</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>1372029.68</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>35.99</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>36.7</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>4.1</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>153670</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>26248</v>
       </c>
     </row>
@@ -1418,36 +1448,39 @@
       <c r="T10" t="n">
         <v>61.85</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>44.55927051671733</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>306</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>1258520.29</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>1473943.68</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>60.44</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>5.74</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>32.47</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>4270</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>1111</v>
       </c>
     </row>
@@ -1511,36 +1544,39 @@
       <c r="T11" t="n">
         <v>58.63</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>157.7476255088195</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>402</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>1677775.19</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>1677279.88</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>54.96</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>14.34</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>15.49</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>3.85</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>24394</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>3933</v>
       </c>
     </row>
@@ -1604,36 +1640,39 @@
       <c r="T12" t="n">
         <v>56.66</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>33.86016148428105</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>546</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>571322.04</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>566293.08</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>8.65</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>11.82</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>34.65</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>3.46</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>12375</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>1477</v>
       </c>
     </row>
@@ -1697,36 +1736,39 @@
       <c r="T13" t="n">
         <v>56.24</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>26.21959280803808</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>186</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>2441803.28</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>2725256.67</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>11.73</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>10.19</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>14.56</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>0.09</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>28011</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>5578</v>
       </c>
     </row>
@@ -1790,36 +1832,39 @@
       <c r="T14" t="n">
         <v>55.15</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U14" t="n">
+        <v>3.156548987525249</v>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>138</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>496415.88</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>483983.21</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>36.74</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>12.61</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>25.23</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>3.81</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>110519</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
         <v>15401</v>
       </c>
     </row>
@@ -1883,36 +1928,39 @@
       <c r="T15" t="n">
         <v>54.11</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U15" t="n">
+        <v>146.3235294117647</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>270</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>1271789.21</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>1382030.89</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>49</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>7.86</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>36.96</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>3.46</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>20487</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
         <v>1919</v>
       </c>
     </row>
@@ -1976,36 +2024,39 @@
       <c r="T16" t="n">
         <v>53.72</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U16" t="n">
+        <v>32.69072290295997</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>228</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>412593.29</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>461362.25</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>63.63</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>5.44</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>31.21</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>1.99</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>109913</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
         <v>15710</v>
       </c>
     </row>
@@ -2069,36 +2120,39 @@
       <c r="T17" t="n">
         <v>53.67</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U17" t="n">
+        <v>30.81124132438275</v>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>432</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>162274.18</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>165749.2</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>36.12</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>12.3</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>5.36</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>12383</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
         <v>1747</v>
       </c>
     </row>
@@ -2162,36 +2216,39 @@
       <c r="T18" t="n">
         <v>47.9</v>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U18" t="n">
+        <v>23.44562391681109</v>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>192</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>222391.83</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>234358.89</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>15.62</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>13.61</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>19.29</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>4.41</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>16536</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AE18" t="n">
         <v>4001</v>
       </c>
     </row>
@@ -2255,36 +2312,39 @@
       <c r="T19" t="n">
         <v>46.85</v>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U19" t="n">
+        <v>135.2030422382181</v>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>366</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>1124597.5</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>1097873.76</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>30.8</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>2.48</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>16.63</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>1.26</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>221113</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
         <v>15547</v>
       </c>
     </row>
@@ -2348,36 +2408,39 @@
       <c r="T20" t="n">
         <v>46.24</v>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U20" t="n">
+        <v>21.72001632557868</v>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>384</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>1503863.63</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
         <v>1891991.87</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
         <v>20.78</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>8.26</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AB20" t="n">
         <v>29.97</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>1.78</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>141858</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AE20" t="n">
         <v>13488</v>
       </c>
     </row>
@@ -2441,36 +2504,39 @@
       <c r="T21" t="n">
         <v>42.86</v>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U21" t="n">
+        <v>19.85162445638271</v>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>486</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
         <v>1191331.95</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
         <v>1268446.56</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Z21" t="n">
         <v>33.32</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
         <v>9.25</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AB21" t="n">
         <v>30.88</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>3.69</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>22240</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AE21" t="n">
         <v>2718</v>
       </c>
     </row>
@@ -2534,36 +2600,39 @@
       <c r="T22" t="n">
         <v>39.36</v>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U22" t="n">
+        <v>28.91484449273394</v>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>372</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>1347046.9</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>1647384.23</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Z22" t="n">
         <v>64.52</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>2.38</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AB22" t="n">
         <v>18.9</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>4.43</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
         <v>35517</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AE22" t="n">
         <v>4585</v>
       </c>
     </row>
@@ -2627,36 +2696,39 @@
       <c r="T23" t="n">
         <v>35.31</v>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U23" t="n">
+        <v>24.27096774193548</v>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>222</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>2521508.87</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
         <v>2620805.22</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
         <v>45.41</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
         <v>14.08</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AB23" t="n">
         <v>30.73</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>2.6</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
         <v>18590</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AE23" t="n">
         <v>1271</v>
       </c>
     </row>
@@ -2671,7 +2743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2694,16 +2766,17 @@
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="7" customWidth="1" min="22" max="22"/>
-    <col width="19" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="33" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
     <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="21" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2809,50 +2882,55 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>return_on_capital_employed_pct</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>broad_sector</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>id_y</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>market_cap_crore</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>enterprise_value_crore</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>pb_ratio</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ev_ebitda</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dividend_yield_pct</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>net_profit</t>
         </is>
@@ -2918,36 +2996,39 @@
       <c r="T2" t="n">
         <v>61.24</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>23.93519910139379</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>300</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>1418164.33</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>1786391.89</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>28.61</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>4.24</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>33.71</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>776352</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>43161</v>
       </c>
     </row>
@@ -3011,36 +3092,39 @@
       <c r="T3" t="n">
         <v>54.87</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>5.748474690927067</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>312</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>2618348.58</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>2449260.08</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>9.81</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>3.91</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>16.66</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>2.82</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>26645</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>6412</v>
       </c>
     </row>
@@ -3104,36 +3188,39 @@
       <c r="T4" t="n">
         <v>43.08</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>2.820446985460198</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>96</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>590971.02</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>656699.3199999999</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>16.89</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>4.15</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>24.7</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>2.62</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>118379</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>18869</v>
       </c>
     </row>
@@ -3197,36 +3284,39 @@
       <c r="T5" t="n">
         <v>37.34</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>20.20662820340802</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>474</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>3154358.33</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>2911084.5</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>25.87</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>1.21</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>26.58</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>3.2</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>20521</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>1733</v>
       </c>
     </row>
@@ -3290,36 +3380,39 @@
       <c r="T6" t="n">
         <v>32.57</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>3.561786022241474</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>288</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>1807433.12</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>1674611.06</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>8.99</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>3.7</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>28.79</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>1.42</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>45748</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>8950</v>
       </c>
     </row>
@@ -3383,36 +3476,39 @@
       <c r="T7" t="n">
         <v>20.18</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>20.2313518675261</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>390</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>146151.16</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>161406.34</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>2.38</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>33.39</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>2.18</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>98692</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>3020</v>
       </c>
     </row>
@@ -3476,36 +3572,39 @@
       <c r="T8" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>14.23726099166652</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>378</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>4173085.48</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>3837414.39</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>14.22</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>29.08</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>2.37</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>139078</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>12270</v>
       </c>
     </row>
@@ -3520,7 +3619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3543,16 +3642,17 @@
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="7" customWidth="1" min="22" max="22"/>
-    <col width="19" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="33" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
     <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="21" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3658,50 +3758,55 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>return_on_capital_employed_pct</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>broad_sector</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>id_y</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>market_cap_crore</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>enterprise_value_crore</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>pb_ratio</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ev_ebitda</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dividend_yield_pct</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>net_profit</t>
         </is>
@@ -3767,36 +3872,39 @@
       <c r="T2" t="n">
         <v>88.88</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>5640.87982832618</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>282</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>1040632.92</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>1061542.29</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>76.23</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>7.87</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>24.64</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>4.27</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>68904</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>8167</v>
       </c>
     </row>
@@ -3860,36 +3968,39 @@
       <c r="T3" t="n">
         <v>63.74</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>5.220349505440574</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>264</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>1319221.86</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>1598760.1</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>25.76</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>6.2</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>38.28</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>3.43</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>159516</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>46081</v>
       </c>
     </row>
@@ -3953,36 +4064,39 @@
       <c r="T4" t="n">
         <v>61.85</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>44.55927051671733</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>306</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>1258520.29</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>1473943.68</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>60.44</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>5.74</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>32.47</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>4270</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>1111</v>
       </c>
     </row>
@@ -4046,36 +4160,39 @@
       <c r="T5" t="n">
         <v>56.88</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>4.887792835880029</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>234</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>808359.03</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>976938.14</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>49.42</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>4.4</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>22.54</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>4.33</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>283649</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>65446</v>
       </c>
     </row>
@@ -4139,36 +4256,39 @@
       <c r="T6" t="n">
         <v>56.66</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>33.86016148428105</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>546</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>571322.04</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>566293.08</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>8.65</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>11.82</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>34.65</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>3.46</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>12375</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>1477</v>
       </c>
     </row>
@@ -4232,36 +4352,39 @@
       <c r="T7" t="n">
         <v>55.15</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>3.156548987525249</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>138</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>496415.88</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>483983.21</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>36.74</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>12.61</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>25.23</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>3.81</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>110519</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>15401</v>
       </c>
     </row>
@@ -4325,36 +4448,39 @@
       <c r="T8" t="n">
         <v>54.87</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>5.748474690927067</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>312</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>2618348.58</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>2449260.08</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>9.81</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>3.91</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>16.66</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>2.82</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>26645</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>6412</v>
       </c>
     </row>
@@ -4418,36 +4544,39 @@
       <c r="T9" t="n">
         <v>43.08</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>2.820446985460198</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>96</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>590971.02</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>656699.3199999999</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>16.89</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>4.15</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>24.7</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>2.62</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>118379</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>18869</v>
       </c>
     </row>
@@ -4511,36 +4640,39 @@
       <c r="T10" t="n">
         <v>39.91</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>4.350587230638684</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>90</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>2473271.58</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>2632574.41</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>69.2</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>4.11</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>15.96</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>0.27</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>54972</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>14451</v>
       </c>
     </row>
@@ -4604,36 +4736,39 @@
       <c r="T11" t="n">
         <v>39.36</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>28.91484449273394</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>372</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>1347046.9</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>1647384.23</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>64.52</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>2.38</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>18.9</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>4.43</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>35517</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>4585</v>
       </c>
     </row>
@@ -4697,36 +4832,39 @@
       <c r="T12" t="n">
         <v>39.29</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>21.23510292524377</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>534</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>1793769.72</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>2116401.21</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>10.13</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>10.51</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>21</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>3.1</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>51084</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>3496</v>
       </c>
     </row>
@@ -4790,36 +4928,39 @@
       <c r="T13" t="n">
         <v>34.86</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>21.28564022809746</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>180</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>3053088.97</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>3624591.94</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>72.53</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>11.71</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>36.84</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>1.94</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>50789</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>2536</v>
       </c>
     </row>
@@ -4883,36 +5024,39 @@
       <c r="T14" t="n">
         <v>34.78</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U14" t="n">
+        <v>4.30488907434453</v>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>480</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>868933.47</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>1098024.4</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>68.53</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>7.91</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>28.82</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>1.86</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>36388</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
         <v>7399</v>
       </c>
     </row>
@@ -4976,36 +5120,39 @@
       <c r="T15" t="n">
         <v>34.32</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U15" t="n">
+        <v>3.495209907313654</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>144</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>971931.96</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>1024979.49</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>16.79</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>10.36</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>13.52</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>2.83</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>19163</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
         <v>3420</v>
       </c>
     </row>
@@ -5069,36 +5216,39 @@
       <c r="T16" t="n">
         <v>34.05</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U16" t="n">
+        <v>11.70643157982139</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>78</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>1905112.17</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>1807796.2</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>15.07</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>6.08</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>39.72</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>2.56</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>110382</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
         <v>15595</v>
       </c>
     </row>
@@ -5162,36 +5312,39 @@
       <c r="T17" t="n">
         <v>33.74</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U17" t="n">
+        <v>11.69243370533429</v>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>498</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>350543.35</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>387549.77</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>54.79</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>7.14</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>24.84</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>1.87</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>15206</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
         <v>1215</v>
       </c>
     </row>
@@ -5255,36 +5408,39 @@
       <c r="T18" t="n">
         <v>32.57</v>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U18" t="n">
+        <v>3.561786022241474</v>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>288</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>1807433.12</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>1674611.06</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>8.99</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>3.7</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>28.79</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>1.42</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>45748</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AE18" t="n">
         <v>8950</v>
       </c>
     </row>
@@ -5348,36 +5504,39 @@
       <c r="T19" t="n">
         <v>30.32</v>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U19" t="n">
+        <v>10.89897112639626</v>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>18</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>187927.97</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>191237.75</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>58.87</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>10.41</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>33.01</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>0.83</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>96421</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
         <v>3335</v>
       </c>
     </row>
@@ -5392,7 +5551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD31"/>
+  <dimension ref="A1:AE31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5415,16 +5574,17 @@
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="7" customWidth="1" min="22" max="22"/>
-    <col width="19" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="33" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
     <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="21" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5530,50 +5690,55 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>return_on_capital_employed_pct</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>broad_sector</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>id_y</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>market_cap_crore</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>enterprise_value_crore</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>pb_ratio</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ev_ebitda</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dividend_yield_pct</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>net_profit</t>
         </is>
@@ -5639,36 +5804,39 @@
       <c r="T2" t="n">
         <v>88.88</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>5640.87982832618</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>282</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>1040632.92</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>1061542.29</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>76.23</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>7.87</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>24.64</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>4.27</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>68904</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>8167</v>
       </c>
     </row>
@@ -5732,36 +5900,39 @@
       <c r="T3" t="n">
         <v>85</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>105.7129732333927</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>156</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>454024.84</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>574785.39</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>34.27</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>14.75</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>25.15</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>4.38</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>142324</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>37369</v>
       </c>
     </row>
@@ -5825,36 +5996,39 @@
       <c r="T4" t="n">
         <v>75</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>4.798373432734667</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>174</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>1381712.03</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>1248409.43</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>46.26</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>14.32</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>10.41</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>2.58</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>6427</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>2724</v>
       </c>
     </row>
@@ -5918,36 +6092,39 @@
       <c r="T5" t="n">
         <v>74.3</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>3027.639751552795</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>216</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>2643616.86</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>3140281.78</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>71.89</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>3.65</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>8.76</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>2.77</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>30381</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>7595</v>
       </c>
     </row>
@@ -6011,36 +6188,39 @@
       <c r="T6" t="n">
         <v>74.08</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>2.876081752900018</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>84</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>2191568.13</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>2726439.01</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>37.73</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>27.47</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>3.37</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>1702</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>7365</v>
       </c>
     </row>
@@ -6101,36 +6281,39 @@
       <c r="T7" t="n">
         <v>69.08</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>39.61352073186944</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>354</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>183583.67</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>205478.22</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>30.67</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>8.1</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>12.21</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>3.77</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>845966</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>40916</v>
       </c>
     </row>
@@ -6194,36 +6377,39 @@
       <c r="T8" t="n">
         <v>67.98999999999999</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>35.77492689368928</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>54</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>2126725.18</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>2475080.63</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>73.37</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>3.9</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>23.94</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>2.42</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>35495</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>5558</v>
       </c>
     </row>
@@ -6287,36 +6473,39 @@
       <c r="T9" t="n">
         <v>66.23</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>19.44697569501501</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>492</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>1339586.09</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>1264175.16</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>37.9</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>6.71</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>21.41</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>3.88</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>48497</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>9610</v>
       </c>
     </row>
@@ -6380,36 +6569,39 @@
       <c r="T10" t="n">
         <v>63.74</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>5.220349505440574</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>264</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>1319221.86</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>1598760.1</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>25.76</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>6.2</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>38.28</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>3.43</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>159516</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>46081</v>
       </c>
     </row>
@@ -6464,36 +6656,39 @@
       <c r="T11" t="n">
         <v>62.29</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>1.120397852630671</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>330</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>1401774.99</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>1814281.53</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>34.24</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>9.91</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>26.41</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>3.09</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>1855</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>1605</v>
       </c>
     </row>
@@ -6557,36 +6752,39 @@
       <c r="T12" t="n">
         <v>58.63</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>157.7476255088195</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>402</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>1677775.19</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>1677279.88</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>54.96</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>14.34</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>15.49</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>3.85</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>24394</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>3933</v>
       </c>
     </row>
@@ -6650,36 +6848,39 @@
       <c r="T13" t="n">
         <v>56.88</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>4.887792835880029</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>234</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>808359.03</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>976938.14</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>49.42</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>4.4</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>22.54</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>4.33</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>283649</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>65446</v>
       </c>
     </row>
@@ -6743,36 +6944,39 @@
       <c r="T14" t="n">
         <v>56.66</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U14" t="n">
+        <v>33.86016148428105</v>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>546</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>571322.04</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>566293.08</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>8.65</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>11.82</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>34.65</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>3.46</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>12375</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
         <v>1477</v>
       </c>
     </row>
@@ -6836,36 +7040,39 @@
       <c r="T15" t="n">
         <v>55.15</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U15" t="n">
+        <v>3.156548987525249</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>138</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>496415.88</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>483983.21</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>36.74</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>12.61</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>25.23</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>3.81</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>110519</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
         <v>15401</v>
       </c>
     </row>
@@ -6929,36 +7136,39 @@
       <c r="T16" t="n">
         <v>54.87</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U16" t="n">
+        <v>5.748474690927067</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>312</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>2618348.58</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>2449260.08</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>9.81</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>3.91</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>16.66</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>2.82</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>26645</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
         <v>6412</v>
       </c>
     </row>
@@ -7022,36 +7232,39 @@
       <c r="T17" t="n">
         <v>54.11</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U17" t="n">
+        <v>146.3235294117647</v>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>270</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>1271789.21</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>1382030.89</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>49</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>7.86</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>36.96</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>3.46</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>20487</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
         <v>1919</v>
       </c>
     </row>
@@ -7115,36 +7328,39 @@
       <c r="T18" t="n">
         <v>53.76</v>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U18" t="n">
+        <v>12.97418225716822</v>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>456</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>432472.71</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>545039.37</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>58.34</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>3.25</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>24.96</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>4.21</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>899041</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AE18" t="n">
         <v>79020</v>
       </c>
     </row>
@@ -7208,36 +7424,39 @@
       <c r="T19" t="n">
         <v>53.73</v>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U19" t="n">
+        <v>28.38958346829047</v>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>72</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>653817.3</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>679803.97</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>29.91</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>9.83</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>20.14</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>3.59</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>44870</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
         <v>7708</v>
       </c>
     </row>
@@ -7295,36 +7514,39 @@
       <c r="T20" t="n">
         <v>52.08</v>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U20" t="n">
+        <v>30.98033093974399</v>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>504</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>1504106.64</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
         <v>1588737.42</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
         <v>67.06999999999999</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>0.93</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AB20" t="n">
         <v>15.35</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>3.65</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>437928</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AE20" t="n">
         <v>31807</v>
       </c>
     </row>
@@ -7388,36 +7610,39 @@
       <c r="T21" t="n">
         <v>48.99</v>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U21" t="n">
+        <v>18.90516562075742</v>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>444</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
         <v>372584.24</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
         <v>410018.95</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Z21" t="n">
         <v>64.39</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
         <v>5.1</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AB21" t="n">
         <v>23.07</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>3.09</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>45843</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AE21" t="n">
         <v>15573</v>
       </c>
     </row>
@@ -7481,36 +7706,39 @@
       <c r="T22" t="n">
         <v>47.9</v>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U22" t="n">
+        <v>23.44562391681109</v>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>192</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>222391.83</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>234358.89</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Z22" t="n">
         <v>15.62</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>13.61</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AB22" t="n">
         <v>19.29</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>4.41</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
         <v>16536</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AE22" t="n">
         <v>4001</v>
       </c>
     </row>
@@ -7574,36 +7802,39 @@
       <c r="T23" t="n">
         <v>42.86</v>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U23" t="n">
+        <v>19.85162445638271</v>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>486</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>1191331.95</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
         <v>1268446.56</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
         <v>33.32</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
         <v>9.25</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AB23" t="n">
         <v>30.88</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>3.69</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
         <v>22240</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AE23" t="n">
         <v>2718</v>
       </c>
     </row>
@@ -7667,36 +7898,39 @@
       <c r="T24" t="n">
         <v>39.36</v>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U24" t="n">
+        <v>28.91484449273394</v>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>372</v>
       </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
         <v>1347046.9</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
         <v>1647384.23</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
         <v>64.52</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
         <v>2.38</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
         <v>18.9</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>4.43</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
         <v>35517</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AE24" t="n">
         <v>4585</v>
       </c>
     </row>
@@ -7760,36 +7994,39 @@
       <c r="T25" t="n">
         <v>39.29</v>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U25" t="n">
+        <v>21.23510292524377</v>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>534</v>
       </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
         <v>1793769.72</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
         <v>2116401.21</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Z25" t="n">
         <v>10.13</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
         <v>10.51</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AB25" t="n">
         <v>21</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
         <v>3.1</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
         <v>51084</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AE25" t="n">
         <v>3496</v>
       </c>
     </row>
@@ -7853,36 +8090,39 @@
       <c r="T26" t="n">
         <v>37.34</v>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U26" t="n">
+        <v>20.20662820340802</v>
+      </c>
+      <c r="V26" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>474</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>3154358.33</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
         <v>2911084.5</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
         <v>25.87</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>1.21</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
         <v>26.58</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>3.2</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AD26" t="n">
         <v>20521</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AE26" t="n">
         <v>1733</v>
       </c>
     </row>
@@ -7946,36 +8186,39 @@
       <c r="T27" t="n">
         <v>35.31</v>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U27" t="n">
+        <v>24.27096774193548</v>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>222</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>2521508.87</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Y27" t="n">
         <v>2620805.22</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Z27" t="n">
         <v>45.41</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>14.08</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AB27" t="n">
         <v>30.73</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
         <v>2.6</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AD27" t="n">
         <v>18590</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AE27" t="n">
         <v>1271</v>
       </c>
     </row>
@@ -8039,36 +8282,39 @@
       <c r="T28" t="n">
         <v>34.64</v>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U28" t="n">
+        <v>17.30975791126167</v>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>120</v>
       </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
         <v>2599556.05</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
         <v>2628370.51</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
         <v>58.43</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>6.47</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
         <v>16.07</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
         <v>4.23</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
         <v>16727</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AE28" t="n">
         <v>2490</v>
       </c>
     </row>
@@ -8132,36 +8378,39 @@
       <c r="T29" t="n">
         <v>26.85</v>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U29" t="n">
+        <v>19.51259271334257</v>
+      </c>
+      <c r="V29" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>48</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>1905622.43</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
         <v>2433382.94</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
         <v>47.72</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>7.68</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AB29" t="n">
         <v>16.74</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
         <v>3.22</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
         <v>19059</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AE29" t="n">
         <v>935</v>
       </c>
     </row>
@@ -8225,36 +8474,39 @@
       <c r="T30" t="n">
         <v>24</v>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U30" t="n">
+        <v>21.36942391594693</v>
+      </c>
+      <c r="V30" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>162</v>
       </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
         <v>56521.84</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
         <v>67755.32000000001</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Z30" t="n">
         <v>50.95</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>13.59</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
         <v>12.02</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AC30" t="n">
         <v>3.42</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AD30" t="n">
         <v>12404</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
         <v>1811</v>
       </c>
     </row>
@@ -8318,36 +8570,39 @@
       <c r="T31" t="n">
         <v>20.18</v>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U31" t="n">
+        <v>20.2313518675261</v>
+      </c>
+      <c r="V31" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>390</v>
       </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
         <v>146151.16</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
         <v>161406.34</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Z31" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>2.38</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>33.39</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
         <v>2.18</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
         <v>98692</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AE31" t="n">
         <v>3020</v>
       </c>
     </row>
@@ -8362,7 +8617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8385,16 +8640,17 @@
     <col width="20" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="7" customWidth="1" min="22" max="22"/>
-    <col width="19" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="33" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
     <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="21" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8500,50 +8756,55 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>return_on_capital_employed_pct</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>broad_sector</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>id_y</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>market_cap_crore</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>enterprise_value_crore</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>pb_ratio</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ev_ebitda</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dividend_yield_pct</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>net_profit</t>
         </is>
@@ -8606,36 +8867,39 @@
       <c r="T2" t="n">
         <v>69.08</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>39.61352073186944</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>354</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>183583.67</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>205478.22</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>30.67</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>8.1</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>12.21</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>3.77</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>845966</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>40916</v>
       </c>
     </row>
@@ -8699,36 +8963,39 @@
       <c r="T3" t="n">
         <v>63.74</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>5.220349505440574</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>264</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>1319221.86</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>1598760.1</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>25.76</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>6.2</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>38.28</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>3.43</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>159516</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>46081</v>
       </c>
     </row>
@@ -8792,36 +9059,39 @@
       <c r="T4" t="n">
         <v>56.88</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>4.887792835880029</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>234</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>808359.03</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>976938.14</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>49.42</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>4.4</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>22.54</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>4.33</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>283649</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>65446</v>
       </c>
     </row>
@@ -8885,36 +9155,39 @@
       <c r="T5" t="n">
         <v>56.73</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>7.234918028249578</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>348</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>430223.52</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>548886.13</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>32.9</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>1.15</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>15.52</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>1.51</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>56237</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>18213</v>
       </c>
     </row>
@@ -8978,36 +9251,39 @@
       <c r="T6" t="n">
         <v>55.15</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>3.156548987525249</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>138</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>496415.88</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>483983.21</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>36.74</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>12.61</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>25.23</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>3.81</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>110519</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>15401</v>
       </c>
     </row>
@@ -9071,36 +9347,39 @@
       <c r="T7" t="n">
         <v>54.87</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>5.748474690927067</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>312</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>2618348.58</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>2449260.08</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>9.81</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>3.91</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>16.66</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>2.82</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>26645</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>6412</v>
       </c>
     </row>
@@ -9164,36 +9443,39 @@
       <c r="T8" t="n">
         <v>54.11</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>146.3235294117647</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>270</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>1271789.21</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>1382030.89</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>49</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>7.86</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>36.96</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>3.46</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>20487</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>1919</v>
       </c>
     </row>
@@ -9257,36 +9539,39 @@
       <c r="T9" t="n">
         <v>47.65</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>1.650120740541991</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>462</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>886097.71</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>1097553.71</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>69.98</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>9.48</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>31.04</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>131988</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>1894</v>
       </c>
     </row>
@@ -9350,36 +9635,39 @@
       <c r="T10" t="n">
         <v>43.08</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>2.820446985460198</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>96</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>590971.02</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>656699.3199999999</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>16.89</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>4.15</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>24.7</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>2.62</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>118379</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>18869</v>
       </c>
     </row>
@@ -9431,36 +9719,36 @@
       <c r="T11" t="n">
         <v>42.16</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>438</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>1825925.6</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>2365495.49</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>19.29</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>10.91</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>23.64</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>1.32</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>109065</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>9157</v>
       </c>
     </row>
@@ -9524,36 +9812,39 @@
       <c r="T12" t="n">
         <v>39.91</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>4.350587230638684</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>90</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>2473271.58</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>2632574.41</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>69.2</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>4.11</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>15.96</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>0.27</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>54972</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>14451</v>
       </c>
     </row>
@@ -9617,36 +9908,39 @@
       <c r="T13" t="n">
         <v>37.39</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>9.29915054435852</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>450</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>291917.42</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>315256.49</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>31.49</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>4.59</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>23.95</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>2.18</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>47517</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>14145</v>
       </c>
     </row>
@@ -9710,36 +10004,39 @@
       <c r="T14" t="n">
         <v>36.72</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U14" t="n">
+        <v>2.612569500628303</v>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>66</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>948868.63</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>929130.29</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>38.14</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>4.66</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>16.87</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>2.32</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>109369</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
         <v>24861</v>
       </c>
     </row>
@@ -9803,36 +10100,39 @@
       <c r="T15" t="n">
         <v>34.78</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U15" t="n">
+        <v>4.30488907434453</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>480</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>868933.47</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>1098024.4</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>68.53</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>7.91</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>28.82</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>1.86</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>36388</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
         <v>7399</v>
       </c>
     </row>
@@ -9896,36 +10196,39 @@
       <c r="T16" t="n">
         <v>34.32</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U16" t="n">
+        <v>3.495209907313654</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>144</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>971931.96</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>1024979.49</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>16.79</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>10.36</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>13.52</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>2.83</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>19163</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
         <v>3420</v>
       </c>
     </row>
@@ -9989,36 +10292,39 @@
       <c r="T17" t="n">
         <v>34.05</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U17" t="n">
+        <v>11.70643157982139</v>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>78</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>1905112.17</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>1807796.2</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>15.07</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>6.08</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>39.72</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>2.56</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>110382</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
         <v>15595</v>
       </c>
     </row>
@@ -10082,36 +10388,39 @@
       <c r="T18" t="n">
         <v>32.57</v>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U18" t="n">
+        <v>3.561786022241474</v>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>288</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>1807433.12</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>1674611.06</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>8.99</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>3.7</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>28.79</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>1.42</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>45748</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AE18" t="n">
         <v>8950</v>
       </c>
     </row>
@@ -10175,36 +10484,39 @@
       <c r="T19" t="n">
         <v>26.48</v>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U19" t="n">
+        <v>3.485901892622634</v>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>426</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>2011885.81</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>2014246.29</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>35.6</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>6.59</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>15.67</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>0.42</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>91508</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
         <v>26461</v>
       </c>
     </row>
@@ -10219,7 +10531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD39"/>
+  <dimension ref="A1:AE39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -10242,16 +10554,17 @@
     <col width="21" customWidth="1" min="18" max="18"/>
     <col width="21" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
-    <col width="7" customWidth="1" min="22" max="22"/>
-    <col width="19" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="33" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="25" customWidth="1" min="25" max="25"/>
     <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="21" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10357,50 +10670,55 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>return_on_capital_employed_pct</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>broad_sector</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>id_y</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>market_cap_crore</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>enterprise_value_crore</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pe_ratio</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>pb_ratio</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ev_ebitda</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dividend_yield_pct</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>net_profit</t>
         </is>
@@ -10466,36 +10784,39 @@
       <c r="T2" t="n">
         <v>88.88</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>5640.87982832618</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>282</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>1040632.92</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>1061542.29</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>76.23</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>7.87</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>24.64</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>4.27</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>68904</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>8167</v>
       </c>
     </row>
@@ -10559,36 +10880,39 @@
       <c r="T3" t="n">
         <v>83.98</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>65.26850065983149</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>522</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>461188.15</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>542230.13</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>78.69</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>6.08</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>29.94</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>240893</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>46099</v>
       </c>
     </row>
@@ -10652,36 +10976,39 @@
       <c r="T4" t="n">
         <v>74.08</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>2.876081752900018</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>84</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>2191568.13</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>2726439.01</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>37.73</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>27.47</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>3.37</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>1702</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>7365</v>
       </c>
     </row>
@@ -10745,36 +11072,39 @@
       <c r="T5" t="n">
         <v>67.98999999999999</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>35.77492689368928</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>54</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>2126725.18</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>2475080.63</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>73.37</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>3.9</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>23.94</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>2.42</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>35495</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>5558</v>
       </c>
     </row>
@@ -10838,36 +11168,39 @@
       <c r="T6" t="n">
         <v>66.73</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>15.24626398560363</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>30</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>675598.01</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>611165.74</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>48.9</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>2.31</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>31.76</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>1.16</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>26711</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>8104</v>
       </c>
     </row>
@@ -10931,36 +11264,39 @@
       <c r="T7" t="n">
         <v>66.23</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>19.44697569501501</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>492</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>1339586.09</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>1264175.16</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>37.9</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>6.71</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>21.41</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>3.88</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>48497</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>9610</v>
       </c>
     </row>
@@ -11024,36 +11360,39 @@
       <c r="T8" t="n">
         <v>65</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>26.2538940548806</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>108</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>378605.83</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>429972.49</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>63.78</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>6.28</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>39.71</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>149982</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>8558</v>
       </c>
     </row>
@@ -11111,36 +11450,39 @@
       <c r="T9" t="n">
         <v>64.38</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>23.44105657077455</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>36</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>1372183.55</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>1357949.64</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>44.57</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>9.91</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>24.76</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>50351</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>20829</v>
       </c>
     </row>
@@ -11204,36 +11546,39 @@
       <c r="T10" t="n">
         <v>64.08</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>118.2077759042966</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>252</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>722281.1</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>656285.92</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>56.45</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>9.32</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>27.63</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>0.98</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>215962</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>10155</v>
       </c>
     </row>
@@ -11297,36 +11642,39 @@
       <c r="T11" t="n">
         <v>63.74</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>5.220349505440574</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>264</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>1319221.86</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>1598760.1</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>25.76</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>6.2</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>38.28</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>3.43</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>159516</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>46081</v>
       </c>
     </row>
@@ -11387,36 +11735,39 @@
       <c r="T12" t="n">
         <v>62.12</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>37.75589530966572</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>294</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>1112279.92</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>1372029.68</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>35.99</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>36.7</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>4.1</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>153670</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>26248</v>
       </c>
     </row>
@@ -11480,36 +11831,39 @@
       <c r="T13" t="n">
         <v>61.85</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>44.55927051671733</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>306</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>1258520.29</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>1473943.68</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>60.44</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>5.74</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>32.47</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>4270</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>1111</v>
       </c>
     </row>
@@ -11573,36 +11927,39 @@
       <c r="T14" t="n">
         <v>58.63</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U14" t="n">
+        <v>157.7476255088195</v>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>402</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>1677775.19</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>1677279.88</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>54.96</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>14.34</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>15.49</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>3.85</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>24394</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
         <v>3933</v>
       </c>
     </row>
@@ -11666,36 +12023,39 @@
       <c r="T15" t="n">
         <v>56.88</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U15" t="n">
+        <v>4.887792835880029</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>234</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>808359.03</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>976938.14</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>49.42</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>4.4</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>22.54</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>4.33</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>283649</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
         <v>65446</v>
       </c>
     </row>
@@ -11759,36 +12119,39 @@
       <c r="T16" t="n">
         <v>56.73</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U16" t="n">
+        <v>7.234918028249578</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>348</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>430223.52</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>548886.13</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>32.9</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>1.15</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AB16" t="n">
         <v>15.52</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>1.51</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>56237</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
         <v>18213</v>
       </c>
     </row>
@@ -11852,36 +12215,39 @@
       <c r="T17" t="n">
         <v>56.66</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U17" t="n">
+        <v>33.86016148428105</v>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>546</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>571322.04</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>566293.08</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>8.65</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>11.82</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>34.65</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>3.46</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>12375</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
         <v>1477</v>
       </c>
     </row>
@@ -11945,36 +12311,39 @@
       <c r="T18" t="n">
         <v>56.24</v>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U18" t="n">
+        <v>26.21959280803808</v>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>186</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>2441803.28</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>2725256.67</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>11.73</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>10.19</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>14.56</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>0.09</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>28011</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AE18" t="n">
         <v>5578</v>
       </c>
     </row>
@@ -12038,36 +12407,39 @@
       <c r="T19" t="n">
         <v>55.15</v>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U19" t="n">
+        <v>3.156548987525249</v>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>138</v>
       </c>
-      <c r="W19" t="n">
+      <c r="X19" t="n">
         <v>496415.88</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
         <v>483983.21</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
         <v>36.74</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>12.61</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>25.23</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>3.81</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>110519</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
         <v>15401</v>
       </c>
     </row>
@@ -12131,36 +12503,39 @@
       <c r="T20" t="n">
         <v>54.87</v>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U20" t="n">
+        <v>5.748474690927067</v>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>312</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>2618348.58</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Y20" t="n">
         <v>2449260.08</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
         <v>9.81</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
         <v>3.91</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AB20" t="n">
         <v>16.66</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>2.82</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>26645</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AE20" t="n">
         <v>6412</v>
       </c>
     </row>
@@ -12224,36 +12599,39 @@
       <c r="T21" t="n">
         <v>54.11</v>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U21" t="n">
+        <v>146.3235294117647</v>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>270</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
         <v>1271789.21</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
         <v>1382030.89</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Z21" t="n">
         <v>49</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="n">
         <v>7.86</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AB21" t="n">
         <v>36.96</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>3.46</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>20487</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AE21" t="n">
         <v>1919</v>
       </c>
     </row>
@@ -12317,36 +12695,39 @@
       <c r="T22" t="n">
         <v>53.72</v>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="U22" t="n">
+        <v>32.69072290295997</v>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>228</v>
       </c>
-      <c r="W22" t="n">
+      <c r="X22" t="n">
         <v>412593.29</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Y22" t="n">
         <v>461362.25</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Z22" t="n">
         <v>63.63</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>5.44</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AB22" t="n">
         <v>31.21</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>1.99</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
         <v>109913</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AE22" t="n">
         <v>15710</v>
       </c>
     </row>
@@ -12410,36 +12791,39 @@
       <c r="T23" t="n">
         <v>53.67</v>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="U23" t="n">
+        <v>30.81124132438275</v>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>432</v>
       </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
         <v>162274.18</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Y23" t="n">
         <v>165749.2</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Z23" t="n">
         <v>36.12</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
         <v>12.3</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AB23" t="n">
         <v>5.36</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
         <v>12383</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AE23" t="n">
         <v>1747</v>
       </c>
     </row>
@@ -12503,36 +12887,39 @@
       <c r="T24" t="n">
         <v>48.23</v>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U24" t="n">
+        <v>754.9037279803359</v>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>276</v>
       </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
         <v>1596987.55</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Y24" t="n">
         <v>2014403.87</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
         <v>20.83</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
         <v>12.38</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
         <v>22.57</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>0.35</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
         <v>90307</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AE24" t="n">
         <v>851</v>
       </c>
     </row>
@@ -12596,36 +12983,39 @@
       <c r="T25" t="n">
         <v>47.9</v>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U25" t="n">
+        <v>23.44562391681109</v>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>192</v>
       </c>
-      <c r="W25" t="n">
+      <c r="X25" t="n">
         <v>222391.83</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Y25" t="n">
         <v>234358.89</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Z25" t="n">
         <v>15.62</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AA25" t="n">
         <v>13.61</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AB25" t="n">
         <v>19.29</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
         <v>4.41</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
         <v>16536</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AE25" t="n">
         <v>4001</v>
       </c>
     </row>
@@ -12689,36 +13079,39 @@
       <c r="T26" t="n">
         <v>46.85</v>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U26" t="n">
+        <v>135.2030422382181</v>
+      </c>
+      <c r="V26" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>366</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>1124597.5</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Y26" t="n">
         <v>1097873.76</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
         <v>30.8</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AA26" t="n">
         <v>2.48</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AB26" t="n">
         <v>16.63</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>1.26</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AD26" t="n">
         <v>221113</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AE26" t="n">
         <v>15547</v>
       </c>
     </row>
@@ -12782,36 +13175,39 @@
       <c r="T27" t="n">
         <v>46.24</v>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="U27" t="n">
+        <v>21.72001632557868</v>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>384</v>
       </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
         <v>1503863.63</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Y27" t="n">
         <v>1891991.87</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Z27" t="n">
         <v>20.78</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AA27" t="n">
         <v>8.26</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AB27" t="n">
         <v>29.97</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
         <v>1.78</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AD27" t="n">
         <v>141858</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AE27" t="n">
         <v>13488</v>
       </c>
     </row>
@@ -12875,36 +13271,39 @@
       <c r="T28" t="n">
         <v>42.86</v>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U28" t="n">
+        <v>19.85162445638271</v>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>486</v>
       </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
         <v>1191331.95</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Y28" t="n">
         <v>1268446.56</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Z28" t="n">
         <v>33.32</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>9.25</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AB28" t="n">
         <v>30.88</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
         <v>3.69</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
         <v>22240</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AE28" t="n">
         <v>2718</v>
       </c>
     </row>
@@ -12968,36 +13367,39 @@
       <c r="T29" t="n">
         <v>39.36</v>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U29" t="n">
+        <v>28.91484449273394</v>
+      </c>
+      <c r="V29" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>372</v>
       </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
         <v>1347046.9</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Y29" t="n">
         <v>1647384.23</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
         <v>64.52</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>2.38</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AB29" t="n">
         <v>18.9</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
         <v>4.43</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
         <v>35517</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AE29" t="n">
         <v>4585</v>
       </c>
     </row>
@@ -13061,36 +13463,39 @@
       <c r="T30" t="n">
         <v>39.29</v>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="U30" t="n">
+        <v>21.23510292524377</v>
+      </c>
+      <c r="V30" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>534</v>
       </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
         <v>1793769.72</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
         <v>2116401.21</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Z30" t="n">
         <v>10.13</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>10.51</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
         <v>21</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AC30" t="n">
         <v>3.1</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AD30" t="n">
         <v>51084</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
         <v>3496</v>
       </c>
     </row>
@@ -13154,36 +13559,39 @@
       <c r="T31" t="n">
         <v>37.34</v>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="U31" t="n">
+        <v>20.20662820340802</v>
+      </c>
+      <c r="V31" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>474</v>
       </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
         <v>3154358.33</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Y31" t="n">
         <v>2911084.5</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Z31" t="n">
         <v>25.87</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>1.21</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>26.58</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
         <v>3.2</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
         <v>20521</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AE31" t="n">
         <v>1733</v>
       </c>
     </row>
@@ -13247,36 +13655,39 @@
       <c r="T32" t="n">
         <v>35.31</v>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U32" t="n">
+        <v>24.27096774193548</v>
+      </c>
+      <c r="V32" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>222</v>
       </c>
-      <c r="W32" t="n">
+      <c r="X32" t="n">
         <v>2521508.87</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Y32" t="n">
         <v>2620805.22</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Z32" t="n">
         <v>45.41</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
         <v>14.08</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AB32" t="n">
         <v>30.73</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AC32" t="n">
         <v>2.6</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AD32" t="n">
         <v>18590</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AE32" t="n">
         <v>1271</v>
       </c>
     </row>
@@ -13340,36 +13751,39 @@
       <c r="T33" t="n">
         <v>34.86</v>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U33" t="n">
+        <v>21.28564022809746</v>
+      </c>
+      <c r="V33" t="inlineStr">
         <is>
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>180</v>
       </c>
-      <c r="W33" t="n">
+      <c r="X33" t="n">
         <v>3053088.97</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Y33" t="n">
         <v>3624591.94</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Z33" t="n">
         <v>72.53</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AA33" t="n">
         <v>11.71</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AB33" t="n">
         <v>36.84</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
         <v>1.94</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AD33" t="n">
         <v>50789</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AE33" t="n">
         <v>2536</v>
       </c>
     </row>
@@ -13433,36 +13847,39 @@
       <c r="T34" t="n">
         <v>33.74</v>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U34" t="n">
+        <v>11.69243370533429</v>
+      </c>
+      <c r="V34" t="inlineStr">
         <is>
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>498</v>
       </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
         <v>350543.35</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Y34" t="n">
         <v>387549.77</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Z34" t="n">
         <v>54.79</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
         <v>7.14</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AB34" t="n">
         <v>24.84</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AC34" t="n">
         <v>1.87</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AD34" t="n">
         <v>15206</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AE34" t="n">
         <v>1215</v>
       </c>
     </row>
@@ -13526,36 +13943,39 @@
       <c r="T35" t="n">
         <v>32.12</v>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U35" t="n">
+        <v>12.93381024077458</v>
+      </c>
+      <c r="V35" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>414</v>
       </c>
-      <c r="W35" t="n">
+      <c r="X35" t="n">
         <v>907823.11</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Y35" t="n">
         <v>1142814.16</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Z35" t="n">
         <v>30.8</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AA35" t="n">
         <v>5.24</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AB35" t="n">
         <v>37.12</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AC35" t="n">
         <v>0.06</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AD35" t="n">
         <v>178501</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AE35" t="n">
         <v>21332</v>
       </c>
     </row>
@@ -13619,36 +14039,39 @@
       <c r="T36" t="n">
         <v>30.82</v>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="U36" t="n">
+        <v>14.48917411505097</v>
+      </c>
+      <c r="V36" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
         <v>198</v>
       </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
         <v>1531867.57</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Y36" t="n">
         <v>1613856.89</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Z36" t="n">
         <v>25.84</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
         <v>9.539999999999999</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AB36" t="n">
         <v>33.07</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AC36" t="n">
         <v>0.31</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AD36" t="n">
         <v>133228</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AE36" t="n">
         <v>9903</v>
       </c>
     </row>
@@ -13712,36 +14135,39 @@
       <c r="T37" t="n">
         <v>26.85</v>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="U37" t="n">
+        <v>19.51259271334257</v>
+      </c>
+      <c r="V37" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="V37" t="n">
+      <c r="W37" t="n">
         <v>48</v>
       </c>
-      <c r="W37" t="n">
+      <c r="X37" t="n">
         <v>1905622.43</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Y37" t="n">
         <v>2433382.94</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Z37" t="n">
         <v>47.72</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
         <v>7.68</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AB37" t="n">
         <v>16.74</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AC37" t="n">
         <v>3.22</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AD37" t="n">
         <v>19059</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AE37" t="n">
         <v>935</v>
       </c>
     </row>
@@ -13805,36 +14231,39 @@
       <c r="T38" t="n">
         <v>26.68</v>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U38" t="n">
+        <v>11.48840296916175</v>
+      </c>
+      <c r="V38" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
         <v>12</v>
       </c>
-      <c r="W38" t="n">
+      <c r="X38" t="n">
         <v>348517.36</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Y38" t="n">
         <v>439276.19</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Z38" t="n">
         <v>58.5</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AA38" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AB38" t="n">
         <v>14.83</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AC38" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AD38" t="n">
         <v>16607</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AE38" t="n">
         <v>1196</v>
       </c>
     </row>
@@ -13898,36 +14327,39 @@
       <c r="T39" t="n">
         <v>26.16</v>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="U39" t="n">
+        <v>12.47602998431054</v>
+      </c>
+      <c r="V39" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
         <v>510</v>
       </c>
-      <c r="W39" t="n">
+      <c r="X39" t="n">
         <v>1647269.48</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Y39" t="n">
         <v>1925345.06</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Z39" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AA39" t="n">
         <v>3.48</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AB39" t="n">
         <v>12.02</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AC39" t="n">
         <v>0.49</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AD39" t="n">
         <v>61449</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AE39" t="n">
         <v>4280</v>
       </c>
     </row>
